--- a/test_cases1.xlsx
+++ b/test_cases1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_files\codes\sessies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_files\codes\profi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F14FEF-5E0F-48E1-B4D2-3898084D2397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD0A7E1-4295-4EF1-86F3-3F0524DB0065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,19 +277,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -665,17 +665,17 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14"/>
+      <c r="D1" s="12"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
       <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -710,13 +710,13 @@
       <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="5"/>
@@ -729,13 +729,13 @@
       <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="7">
         <v>123</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="5"/>
@@ -749,10 +749,11 @@
       <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="10"/>
@@ -767,17 +768,17 @@
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -793,7 +794,7 @@
       <c r="D10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -812,35 +813,36 @@
       <c r="D11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="7">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="7">
         <v>123</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
